--- a/data/trans_orig/IP18A03-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP18A03-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17278</t>
+          <t>17076</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27952</t>
+          <t>27861</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28278</t>
+          <t>28240</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39197</t>
+          <t>39208</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48583</t>
+          <t>48050</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64703</t>
+          <t>64200</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>62,78%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22289</t>
+          <t>22380</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32963</t>
+          <t>33165</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12820</t>
+          <t>12809</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23739</t>
+          <t>23777</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37555</t>
+          <t>38058</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53675</t>
+          <t>54208</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>53,01%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58068</t>
+          <t>58724</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72832</t>
+          <t>72047</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57985</t>
+          <t>58129</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72648</t>
+          <t>72959</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>121309</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>141107</t>
+          <t>142305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>75,6%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18718</t>
+          <t>19503</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33482</t>
+          <t>32826</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24024</t>
+          <t>23713</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38687</t>
+          <t>38543</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47115</t>
+          <t>45917</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>66913</t>
+          <t>66400</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,28%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41178</t>
+          <t>40671</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52505</t>
+          <t>52213</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43951</t>
+          <t>43997</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54719</t>
+          <t>54726</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>88389</t>
+          <t>88236</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104909</t>
+          <t>104609</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,16%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10846</t>
+          <t>11138</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22173</t>
+          <t>22680</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12433</t>
+          <t>12426</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23201</t>
+          <t>23155</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25594</t>
+          <t>25894</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>42114</t>
+          <t>42267</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,39%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37418</t>
+          <t>36994</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50051</t>
+          <t>49729</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37580</t>
+          <t>37743</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50491</t>
+          <t>50579</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>78948</t>
+          <t>78749</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96910</t>
+          <t>96516</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,4%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17345</t>
+          <t>17667</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29978</t>
+          <t>30402</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17282</t>
+          <t>17194</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30193</t>
+          <t>30030</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38259</t>
+          <t>38653</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>56221</t>
+          <t>56420</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,74%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9297</t>
+          <t>8942</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18317</t>
+          <t>18278</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14041</t>
+          <t>13728</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23456</t>
+          <t>23031</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25525</t>
+          <t>25943</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39392</t>
+          <t>38756</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>60,3%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13792</t>
+          <t>13831</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22812</t>
+          <t>23167</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8709</t>
+          <t>9134</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18124</t>
+          <t>18437</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24883</t>
+          <t>25519</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38750</t>
+          <t>38332</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>59,64%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33309</t>
+          <t>33231</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43409</t>
+          <t>43494</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30222</t>
+          <t>30308</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40789</t>
+          <t>40751</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>67791</t>
+          <t>67700</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81745</t>
+          <t>82026</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,48%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>7613</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17798</t>
+          <t>17876</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10021</t>
+          <t>10059</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20588</t>
+          <t>20502</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20172</t>
+          <t>19891</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>34126</t>
+          <t>34217</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,57%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>77271</t>
+          <t>76136</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>93210</t>
+          <t>93002</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>74336</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>90591</t>
+          <t>91280</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>154382</t>
+          <t>155559</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>177888</t>
+          <t>178709</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,8%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28411</t>
+          <t>28619</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>44350</t>
+          <t>45485</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>33258</t>
+          <t>32569</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>50359</t>
+          <t>49513</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>67583</t>
+          <t>66762</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>91089</t>
+          <t>89912</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>36,63%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>50509</t>
+          <t>49954</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>67481</t>
+          <t>67570</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>60089</t>
+          <t>60179</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>78761</t>
+          <t>78559</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>116097</t>
+          <t>117126</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>141730</t>
+          <t>141824</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>55,79%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>53161</t>
+          <t>53072</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>70133</t>
+          <t>70688</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>54814</t>
+          <t>55016</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>73486</t>
+          <t>73396</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>112487</t>
+          <t>112393</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>138120</t>
+          <t>137091</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>53,93%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>356422</t>
+          <t>357395</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>394946</t>
+          <t>395617</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>380118</t>
+          <t>382268</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>422228</t>
+          <t>419985</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>750925</t>
+          <t>748592</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>804747</t>
+          <t>803506</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,75%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>203072</t>
+          <t>202401</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>241596</t>
+          <t>240623</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>201786</t>
+          <t>204029</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>243896</t>
+          <t>241746</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>417285</t>
+          <t>418526</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>471107</t>
+          <t>473440</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,74%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29546</t>
+          <t>29443</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40386</t>
+          <t>40828</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33660</t>
+          <t>33382</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45414</t>
+          <t>45420</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>66289</t>
+          <t>66653</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83294</t>
+          <t>82997</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,08%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11510</t>
+          <t>11068</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22350</t>
+          <t>22453</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13239</t>
+          <t>13233</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24993</t>
+          <t>25271</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27254</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44259</t>
+          <t>43895</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>39,71%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60883</t>
+          <t>60190</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75215</t>
+          <t>74957</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66348</t>
+          <t>67050</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79684</t>
+          <t>80563</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>132512</t>
+          <t>133566</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>152830</t>
+          <t>152703</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>78,95%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20068</t>
+          <t>20326</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34400</t>
+          <t>35093</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18449</t>
+          <t>17570</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31785</t>
+          <t>31083</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>40586</t>
+          <t>40713</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>60904</t>
+          <t>59850</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>30,94%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30492</t>
+          <t>30276</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45159</t>
+          <t>43906</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31366</t>
+          <t>32525</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45309</t>
+          <t>46167</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66875</t>
+          <t>67229</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85798</t>
+          <t>86247</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,49%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22255</t>
+          <t>23508</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36922</t>
+          <t>37138</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25294</t>
+          <t>24436</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39237</t>
+          <t>38078</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>52218</t>
+          <t>51769</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>71141</t>
+          <t>70787</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,29%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52504</t>
+          <t>52946</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63534</t>
+          <t>63884</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55699</t>
+          <t>55987</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68217</t>
+          <t>67813</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>112593</t>
+          <t>112057</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>129064</t>
+          <t>129658</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,55%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8800</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19830</t>
+          <t>19388</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11012</t>
+          <t>11416</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23530</t>
+          <t>23242</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22499</t>
+          <t>21905</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>38970</t>
+          <t>39506</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31371</t>
+          <t>31531</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38118</t>
+          <t>38105</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27585</t>
+          <t>27785</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37289</t>
+          <t>37348</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62432</t>
+          <t>62769</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74131</t>
+          <t>74262</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,69%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8153</t>
+          <t>7993</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5990</t>
+          <t>5931</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15694</t>
+          <t>15494</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8672</t>
+          <t>8541</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20371</t>
+          <t>20034</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,2%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25041</t>
+          <t>24074</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36828</t>
+          <t>36479</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22646</t>
+          <t>22910</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35744</t>
+          <t>35963</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50823</t>
+          <t>51091</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67915</t>
+          <t>68046</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,51%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18431</t>
+          <t>18780</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30218</t>
+          <t>31185</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23336</t>
+          <t>23117</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36434</t>
+          <t>36170</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>46424</t>
+          <t>46293</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>63516</t>
+          <t>63248</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>55,32%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59228</t>
+          <t>59587</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>78072</t>
+          <t>77978</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>68212</t>
+          <t>67796</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>87650</t>
+          <t>87865</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>132705</t>
+          <t>133790</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>159853</t>
+          <t>160798</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>58,1%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>56278</t>
+          <t>56372</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>75122</t>
+          <t>74763</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>54784</t>
+          <t>54569</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>74222</t>
+          <t>74638</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>116931</t>
+          <t>115986</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>144079</t>
+          <t>142994</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>51,66%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>90824</t>
+          <t>89545</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>109744</t>
+          <t>108919</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>103947</t>
+          <t>103797</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>122564</t>
+          <t>121869</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>198596</t>
+          <t>199375</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>225848</t>
+          <t>227221</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,65%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>42215</t>
+          <t>43040</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>61135</t>
+          <t>62414</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>38258</t>
+          <t>38953</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>56875</t>
+          <t>57025</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>86933</t>
+          <t>85560</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>114185</t>
+          <t>113406</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,26%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>413497</t>
+          <t>415593</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>454263</t>
+          <t>454096</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>447890</t>
+          <t>446708</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>490760</t>
+          <t>490247</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>875216</t>
+          <t>874944</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>931656</t>
+          <t>933318</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,62%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>213756</t>
+          <t>213923</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>254522</t>
+          <t>252426</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>221472</t>
+          <t>221985</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>264342</t>
+          <t>265524</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>448595</t>
+          <t>446933</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>505035</t>
+          <t>505307</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,61%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35237</t>
+          <t>35002</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44816</t>
+          <t>44802</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33342</t>
+          <t>33282</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44548</t>
+          <t>44676</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71690</t>
+          <t>72663</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86804</t>
+          <t>87933</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>79,66%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8653</t>
+          <t>8667</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18232</t>
+          <t>18467</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12368</t>
+          <t>12240</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23574</t>
+          <t>23634</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23581</t>
+          <t>22452</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>37722</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>34,17%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60725</t>
+          <t>60872</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73499</t>
+          <t>73273</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62095</t>
+          <t>61412</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76114</t>
+          <t>75797</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>126249</t>
+          <t>126309</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>145152</t>
+          <t>146475</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>79,51%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16249</t>
+          <t>16475</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29023</t>
+          <t>28876</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18356</t>
+          <t>18673</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32375</t>
+          <t>33058</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39066</t>
+          <t>37743</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>57969</t>
+          <t>57909</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,43%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38243</t>
+          <t>39085</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51539</t>
+          <t>52121</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42833</t>
+          <t>43417</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52975</t>
+          <t>53529</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84807</t>
+          <t>86221</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>102708</t>
+          <t>103024</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,42%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14528</t>
+          <t>13946</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27824</t>
+          <t>26982</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9060</t>
+          <t>8506</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19202</t>
+          <t>18618</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25394</t>
+          <t>25078</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43295</t>
+          <t>41881</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>32,69%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46387</t>
+          <t>45930</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59417</t>
+          <t>58882</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50346</t>
+          <t>49819</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64179</t>
+          <t>64017</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>100282</t>
+          <t>101195</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>120127</t>
+          <t>119903</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,68%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13844</t>
+          <t>14379</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26874</t>
+          <t>27331</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14956</t>
+          <t>15118</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28789</t>
+          <t>29316</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32270</t>
+          <t>32494</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52115</t>
+          <t>51202</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>33,6%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24805</t>
+          <t>24522</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34332</t>
+          <t>34005</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23271</t>
+          <t>23058</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33456</t>
+          <t>33320</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>50999</t>
+          <t>50517</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>65350</t>
+          <t>65850</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,96%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7477</t>
+          <t>7804</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17004</t>
+          <t>17287</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11426</t>
+          <t>11562</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21611</t>
+          <t>21824</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21342</t>
+          <t>20842</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35693</t>
+          <t>36175</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,73%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30919</t>
+          <t>30446</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41899</t>
+          <t>41450</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33442</t>
+          <t>33844</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44926</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>67867</t>
+          <t>67827</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>83937</t>
+          <t>82966</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>75,94%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10329</t>
+          <t>10778</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21309</t>
+          <t>21782</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12098</t>
+          <t>12042</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23582</t>
+          <t>23180</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>25315</t>
+          <t>26286</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>41385</t>
+          <t>41425</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,92%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40039</t>
+          <t>40549</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57108</t>
+          <t>57555</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43182</t>
+          <t>44145</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61618</t>
+          <t>61334</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>89252</t>
+          <t>89116</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>113129</t>
+          <t>112862</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,39%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>54438</t>
+          <t>53991</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>71507</t>
+          <t>70997</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>50813</t>
+          <t>51097</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>69249</t>
+          <t>68286</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>110848</t>
+          <t>111115</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>134725</t>
+          <t>134861</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,21%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>88479</t>
+          <t>88520</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>108554</t>
+          <t>108094</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>88302</t>
+          <t>89237</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>108777</t>
+          <t>109396</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>184329</t>
+          <t>184063</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>212886</t>
+          <t>211010</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,1%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>50594</t>
+          <t>51054</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>70669</t>
+          <t>70628</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>56230</t>
+          <t>55611</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>76705</t>
+          <t>75770</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>111269</t>
+          <t>113145</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>139826</t>
+          <t>140092</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,22%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>401597</t>
+          <t>402102</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>440376</t>
+          <t>441011</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>415013</t>
+          <t>415971</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>455541</t>
+          <t>454660</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>827832</t>
+          <t>828723</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>884042</t>
+          <t>884751</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>67,07%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>206901</t>
+          <t>206266</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>245680</t>
+          <t>245175</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>216360</t>
+          <t>217241</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>256888</t>
+          <t>255930</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>435136</t>
+          <t>434427</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>491346</t>
+          <t>490455</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,18%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7172</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11503</t>
+          <t>11488</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9557</t>
+          <t>9480</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13655</t>
+          <t>13658</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18524</t>
+          <t>18571</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24686</t>
+          <t>24638</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,2%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>603</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>5208</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>406</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4507</t>
+          <t>4584</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7584</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>28,99%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8660</t>
+          <t>8677</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13207</t>
+          <t>13232</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13295</t>
+          <t>12974</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15984</t>
+          <t>15978</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23352</t>
+          <t>22861</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28771</t>
+          <t>28774</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>397</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>352</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6607</t>
+          <t>7098</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>23,69%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8848</t>
+          <t>9641</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13405</t>
+          <t>13429</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11928</t>
+          <t>11621</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16091</t>
+          <t>16037</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22870</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29016</t>
+          <t>29024</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>528</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4494</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7509</t>
+          <t>7013</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>23,08%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6576</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12403</t>
+          <t>12504</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9289</t>
+          <t>9525</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14261</t>
+          <t>14272</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18648</t>
+          <t>18481</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26013</t>
+          <t>26106</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,36%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>764</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6692</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>423</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5406</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1857</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9315</t>
+          <t>9482</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,91%</t>
         </is>
       </c>
     </row>
@@ -12109,7 +12109,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2294</t>
+          <t>2372</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5293</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8831</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,69%</t>
         </is>
       </c>
     </row>
@@ -12227,7 +12227,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3063</t>
+          <t>2985</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12242,7 +12242,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>495</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4031</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>42,94%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5144</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8785</t>
+          <t>8772</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11146</t>
+          <t>10928</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16144</t>
+          <t>15911</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17921</t>
+          <t>18190</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24180</t>
+          <t>24166</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,28%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>361</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>6127</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8267</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>30,54%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13265</t>
+          <t>13410</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20486</t>
+          <t>20434</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17401</t>
+          <t>16994</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24771</t>
+          <t>24949</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33607</t>
+          <t>33469</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43689</t>
+          <t>43571</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,11%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>1857</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9026</t>
+          <t>8881</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2955</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>10732</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6328</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>16410</t>
+          <t>16548</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>33,08%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>2681</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7333</t>
+          <t>7811</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5807</t>
+          <t>5617</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13003</t>
+          <t>12890</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10035</t>
+          <t>9727</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18911</t>
+          <t>18684</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>58,53%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>4167</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9458</t>
+          <t>9297</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>14135</t>
+          <t>14325</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>13009</t>
+          <t>13236</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>21885</t>
+          <t>22193</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>69,53%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>69996</t>
+          <t>69339</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>84020</t>
+          <t>83614</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>96721</t>
+          <t>97109</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>111564</t>
+          <t>111974</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>170762</t>
+          <t>170971</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>191593</t>
+          <t>192659</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>83,08%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>16294</t>
+          <t>16700</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>30318</t>
+          <t>30975</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>20028</t>
+          <t>19618</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>34871</t>
+          <t>34483</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>40313</t>
+          <t>39247</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>61144</t>
+          <t>60935</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>
